--- a/AAII_Financials/Quarterly/OCG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OCG_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
   <si>
     <t>OCG</t>
   </si>
@@ -1102,8 +1102,8 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
+      <c r="D17" s="3">
+        <v>3200</v>
       </c>
       <c r="E17" s="3">
         <v>3300</v>
@@ -1149,8 +1149,8 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-2400</v>
       </c>
       <c r="E18" s="3">
         <v>-2500</v>
@@ -1215,8 +1215,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>300</v>
       </c>
       <c r="E20" s="3">
         <v>100</v>
@@ -1497,8 +1497,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>-2100</v>
       </c>
       <c r="E26" s="3">
         <v>-2400</v>
@@ -1544,8 +1544,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>-2100</v>
       </c>
       <c r="E27" s="3">
         <v>-2400</v>
@@ -1779,8 +1779,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-300</v>
       </c>
       <c r="E32" s="3">
         <v>-100</v>
@@ -1826,8 +1826,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>-2100</v>
       </c>
       <c r="E33" s="3">
         <v>-2400</v>
@@ -1920,8 +1920,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>-2100</v>
       </c>
       <c r="E35" s="3">
         <v>-2400</v>
@@ -2057,8 +2057,8 @@
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>3</v>
+      <c r="D41" s="3">
+        <v>21600</v>
       </c>
       <c r="E41" s="3">
         <v>17200</v>
@@ -2151,8 +2151,8 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>3</v>
+      <c r="D43" s="3">
+        <v>1200</v>
       </c>
       <c r="E43" s="3">
         <v>7900</v>
@@ -2245,8 +2245,8 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>16100</v>
       </c>
       <c r="E45" s="3">
         <v>17100</v>
@@ -2292,8 +2292,8 @@
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>3</v>
+      <c r="D46" s="3">
+        <v>38900</v>
       </c>
       <c r="E46" s="3">
         <v>42200</v>
@@ -2339,8 +2339,8 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>3</v>
+      <c r="D47" s="3">
+        <v>900</v>
       </c>
       <c r="E47" s="3">
         <v>900</v>
@@ -2386,8 +2386,8 @@
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>3</v>
+      <c r="D48" s="3">
+        <v>9100</v>
       </c>
       <c r="E48" s="3">
         <v>9500</v>
@@ -2433,8 +2433,8 @@
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>3</v>
+      <c r="D49" s="3">
+        <v>700</v>
       </c>
       <c r="E49" s="3">
         <v>800</v>
@@ -2753,8 +2753,8 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>3</v>
+      <c r="D57" s="3">
+        <v>2400</v>
       </c>
       <c r="E57" s="3">
         <v>3000</v>
@@ -2847,8 +2847,8 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>600</v>
       </c>
       <c r="E59" s="3">
         <v>800</v>
@@ -2894,8 +2894,8 @@
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>3</v>
+      <c r="D60" s="3">
+        <v>3000</v>
       </c>
       <c r="E60" s="3">
         <v>3800</v>
@@ -2988,8 +2988,8 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>3</v>
+      <c r="D62" s="3">
+        <v>0</v>
       </c>
       <c r="E62" s="3">
         <v>0</v>
@@ -3176,8 +3176,8 @@
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>3</v>
+      <c r="D66" s="3">
+        <v>3000</v>
       </c>
       <c r="E66" s="3">
         <v>3800</v>
@@ -3430,8 +3430,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>3</v>
+      <c r="D72" s="3">
+        <v>26300</v>
       </c>
       <c r="E72" s="3">
         <v>28400</v>
@@ -3764,8 +3764,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>-2100</v>
       </c>
       <c r="E81" s="3">
         <v>-2400</v>

--- a/AAII_Financials/Quarterly/OCG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OCG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
   <si>
     <t>OCG</t>
   </si>
@@ -656,85 +656,89 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44196</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44012</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43830</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43646</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43465</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43281</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -745,34 +749,34 @@
         <v>800</v>
       </c>
       <c r="F8" s="3">
+        <v>800</v>
+      </c>
+      <c r="G8" s="3">
         <v>17000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>24500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>15000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5400</v>
       </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
+      <c r="O8" s="3">
+        <v>0</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
@@ -780,8 +784,11 @@
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -789,37 +796,37 @@
         <v>200</v>
       </c>
       <c r="E9" s="3">
+        <v>200</v>
+      </c>
+      <c r="F9" s="3">
         <v>-100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>500</v>
       </c>
-      <c r="N9" s="3">
-        <v>0</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
+      <c r="O9" s="3">
+        <v>0</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
@@ -827,8 +834,11 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -836,37 +846,37 @@
         <v>600</v>
       </c>
       <c r="E10" s="3">
+        <v>600</v>
+      </c>
+      <c r="F10" s="3">
         <v>900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>15900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>12100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>23100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>12800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>12100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>7300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4900</v>
       </c>
-      <c r="N10" s="3">
-        <v>0</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
+      <c r="O10" s="3">
+        <v>0</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
@@ -874,8 +884,11 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -893,8 +906,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -940,8 +954,11 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -987,8 +1004,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1034,8 +1054,11 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1081,8 +1104,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1097,46 +1123,47 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E17" s="3">
         <v>3200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3300</v>
-      </c>
-      <c r="F17" s="3">
-        <v>12000</v>
       </c>
       <c r="G17" s="3">
         <v>12000</v>
       </c>
       <c r="H17" s="3">
+        <v>12000</v>
+      </c>
+      <c r="I17" s="3">
         <v>14700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2700</v>
       </c>
-      <c r="N17" s="3">
-        <v>0</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
+      <c r="O17" s="3">
+        <v>0</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
@@ -1144,46 +1171,49 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-2400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-2500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>9800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>8900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2700</v>
       </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
+      <c r="O18" s="3">
+        <v>0</v>
       </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
@@ -1191,8 +1221,11 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1210,46 +1243,47 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>500</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
-      </c>
-      <c r="H20" s="3">
-        <v>300</v>
       </c>
       <c r="I20" s="3">
         <v>300</v>
       </c>
       <c r="J20" s="3">
+        <v>300</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
+      <c r="O20" s="3">
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
@@ -1257,8 +1291,11 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1277,26 +1314,26 @@
       <c r="H21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I21" s="3">
+      <c r="I21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J21" s="3">
         <v>2000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2700</v>
       </c>
-      <c r="N21" s="3">
-        <v>0</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
+      <c r="O21" s="3">
+        <v>0</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
@@ -1304,8 +1341,11 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1351,46 +1391,49 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>10100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>9100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2600</v>
       </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
+      <c r="O23" s="3">
+        <v>0</v>
       </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
@@ -1398,8 +1441,11 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1418,11 +1464,11 @@
       <c r="H24" s="3">
         <v>0</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1436,8 +1482,8 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
+      <c r="O24" s="3">
+        <v>0</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
@@ -1445,8 +1491,11 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1492,46 +1541,49 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>10100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>9100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2600</v>
       </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
+      <c r="O26" s="3">
+        <v>0</v>
       </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
@@ -1539,46 +1591,49 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>10100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>9100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2600</v>
       </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
+      <c r="O27" s="3">
+        <v>0</v>
       </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
@@ -1586,8 +1641,11 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1633,8 +1691,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1680,8 +1741,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1727,8 +1791,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1774,46 +1841,49 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-300</v>
       </c>
       <c r="I32" s="3">
         <v>-300</v>
       </c>
       <c r="J32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
+      <c r="O32" s="3">
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
@@ -1821,46 +1891,49 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>10100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>9100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2600</v>
       </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
+      <c r="O33" s="3">
+        <v>0</v>
       </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
@@ -1868,8 +1941,11 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1915,46 +1991,49 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>10100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>9100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2600</v>
       </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
+      <c r="O35" s="3">
+        <v>0</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
@@ -1962,60 +2041,66 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44196</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44012</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43830</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43646</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43465</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43281</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2033,8 +2118,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2052,40 +2138,41 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E41" s="3">
         <v>21600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>17200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>38700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>29400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>42600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>18200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>400</v>
-      </c>
-      <c r="K41" s="3">
-        <v>9200</v>
       </c>
       <c r="L41" s="3">
         <v>9200</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
+      <c r="M41" s="3">
+        <v>9200</v>
       </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
@@ -2099,38 +2186,41 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E42" s="3">
-        <v>0</v>
+      <c r="D42" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>1900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>17500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>9800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1700</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2146,41 +2236,44 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>500</v>
+      </c>
+      <c r="E43" s="3">
         <v>1200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>5000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>300</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2193,8 +2286,11 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2240,41 +2336,44 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E45" s="3">
         <v>16100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>17100</v>
-      </c>
-      <c r="F45" s="3">
-        <v>600</v>
       </c>
       <c r="G45" s="3">
         <v>600</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="H45" s="3">
+        <v>600</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>2900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>600</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2287,41 +2386,44 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E46" s="3">
         <v>38900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>42200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>46200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>36100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>47200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>39000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9500</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2334,8 +2436,11 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2346,13 +2451,13 @@
         <v>900</v>
       </c>
       <c r="F47" s="3">
+        <v>900</v>
+      </c>
+      <c r="G47" s="3">
         <v>1000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3700</v>
-      </c>
-      <c r="H47" s="3">
-        <v>500</v>
       </c>
       <c r="I47" s="3">
         <v>500</v>
@@ -2366,8 +2471,8 @@
       <c r="L47" s="3">
         <v>500</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
+      <c r="M47" s="3">
+        <v>500</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
@@ -2381,40 +2486,43 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E48" s="3">
         <v>9100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>9500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>9600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>9900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>800</v>
-      </c>
-      <c r="I48" s="3">
-        <v>400</v>
       </c>
       <c r="J48" s="3">
         <v>400</v>
       </c>
       <c r="K48" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="L48" s="3">
         <v>500</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
+      <c r="M48" s="3">
+        <v>500</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
@@ -2428,41 +2536,44 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>500</v>
+      </c>
+      <c r="E49" s="3">
         <v>700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>600</v>
-      </c>
-      <c r="J49" s="3">
-        <v>700</v>
       </c>
       <c r="K49" s="3">
         <v>700</v>
       </c>
       <c r="L49" s="3">
+        <v>700</v>
+      </c>
+      <c r="M49" s="3">
         <v>800</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2475,8 +2586,11 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2522,8 +2636,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2569,13 +2686,16 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>100</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>3</v>
@@ -2583,27 +2703,27 @@
       <c r="F52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
         <v>1500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>700</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2616,8 +2736,11 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2663,41 +2786,44 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>48600</v>
+      </c>
+      <c r="E54" s="3">
         <v>49500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>53400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>57700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>50800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>50500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>41100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12000</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2710,8 +2836,11 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2729,8 +2858,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2748,41 +2878,42 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E57" s="3">
         <v>2400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>300</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2795,8 +2926,11 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2842,41 +2976,44 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>500</v>
+      </c>
+      <c r="E59" s="3">
         <v>600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1400</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2889,41 +3026,44 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E60" s="3">
         <v>3000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1700</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2936,8 +3076,11 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2983,8 +3126,11 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2997,8 +3143,8 @@
       <c r="F62" s="3">
         <v>0</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
+      <c r="G62" s="3">
+        <v>0</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -3015,8 +3161,8 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -3030,8 +3176,11 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3077,8 +3226,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3124,8 +3276,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3171,41 +3326,44 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E66" s="3">
         <v>3000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1700</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3218,8 +3376,11 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3237,8 +3398,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3284,8 +3446,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3331,8 +3496,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3378,8 +3546,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3425,41 +3596,44 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E72" s="3">
         <v>26300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>28400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>30800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>25200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>23800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>13800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>12100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>11700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>8900</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3472,8 +3646,11 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3519,8 +3696,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3566,8 +3746,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3613,41 +3796,44 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>45500</v>
+      </c>
+      <c r="E76" s="3">
         <v>46500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>49600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>52600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>47200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>43600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>33600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10300</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3660,8 +3846,11 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3707,98 +3896,104 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44196</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44012</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43830</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43646</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43465</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43281</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>10100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>9100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2600</v>
       </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
+      <c r="O81" s="3">
+        <v>0</v>
       </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
@@ -3806,8 +4001,11 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3825,31 +4023,32 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3">
+        <v>0</v>
+      </c>
+      <c r="G83" s="3">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <v>0</v>
       </c>
       <c r="I83" s="3">
-        <v>300</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3872,8 +4071,11 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3919,8 +4121,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3966,8 +4171,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4013,8 +4221,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4060,8 +4271,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4107,31 +4321,34 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
+        <v>0</v>
       </c>
       <c r="I89" s="3">
-        <v>8100</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
+        <v>0</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -4154,8 +4371,11 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4173,8 +4393,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4202,8 +4423,8 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
+      <c r="L91" s="3">
+        <v>0</v>
       </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
@@ -4220,8 +4441,11 @@
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4267,8 +4491,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4314,31 +4541,34 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
+        <v>0</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3">
+        <v>0</v>
       </c>
       <c r="I94" s="3">
-        <v>-11800</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -4361,8 +4591,11 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4380,8 +4613,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4427,8 +4661,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4474,8 +4711,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4521,8 +4761,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4568,31 +4811,34 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
       </c>
       <c r="I100" s="3">
-        <v>18100</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -4615,31 +4861,34 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
       </c>
       <c r="I101" s="3">
-        <v>500</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -4662,31 +4911,34 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
+      <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
       </c>
       <c r="I102" s="3">
-        <v>14900</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
@@ -4707,6 +4959,9 @@
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OCG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OCG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="92">
   <si>
     <t>OCG</t>
   </si>
@@ -656,239 +656,264 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44377</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44196</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44012</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>43830</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43646</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43465</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43281</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="E8" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="F8" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="G8" s="3">
-        <v>17000</v>
+        <v>400</v>
       </c>
       <c r="H8" s="3">
-        <v>13100</v>
+        <v>400</v>
       </c>
       <c r="I8" s="3">
+        <v>400</v>
+      </c>
+      <c r="J8" s="3">
+        <v>400</v>
+      </c>
+      <c r="K8" s="3">
         <v>24500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>15000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>2500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>13400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>7900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>5400</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
+      <c r="Q8" s="3">
+        <v>0</v>
       </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E9" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F9" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="G9" s="3">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="H9" s="3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="I9" s="3">
+        <v>100</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
         <v>1400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>2200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>500</v>
       </c>
-      <c r="O9" s="3">
-        <v>0</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
+      <c r="Q9" s="3">
+        <v>0</v>
       </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="E10" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="F10" s="3">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="G10" s="3">
-        <v>15900</v>
+        <v>300</v>
       </c>
       <c r="H10" s="3">
+        <v>300</v>
+      </c>
+      <c r="I10" s="3">
+        <v>300</v>
+      </c>
+      <c r="J10" s="3">
+        <v>400</v>
+      </c>
+      <c r="K10" s="3">
+        <v>23100</v>
+      </c>
+      <c r="L10" s="3">
+        <v>12800</v>
+      </c>
+      <c r="M10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="N10" s="3">
         <v>12100</v>
       </c>
-      <c r="I10" s="3">
-        <v>23100</v>
-      </c>
-      <c r="J10" s="3">
-        <v>12800</v>
-      </c>
-      <c r="K10" s="3">
-        <v>2100</v>
-      </c>
-      <c r="L10" s="3">
-        <v>12100</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>7300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>4900</v>
       </c>
-      <c r="O10" s="3">
-        <v>0</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
+      <c r="Q10" s="3">
+        <v>0</v>
       </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -907,8 +932,10 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -957,8 +984,14 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1007,16 +1040,22 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -1031,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1057,31 +1096,37 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1107,8 +1152,14 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1124,108 +1175,122 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K17" s="3">
+        <v>14700</v>
+      </c>
+      <c r="L17" s="3">
+        <v>13600</v>
+      </c>
+      <c r="M17" s="3">
+        <v>2200</v>
+      </c>
+      <c r="N17" s="3">
+        <v>4500</v>
+      </c>
+      <c r="O17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="P17" s="3">
         <v>2700</v>
       </c>
-      <c r="E17" s="3">
-        <v>3200</v>
-      </c>
-      <c r="F17" s="3">
-        <v>3300</v>
-      </c>
-      <c r="G17" s="3">
-        <v>12000</v>
-      </c>
-      <c r="H17" s="3">
-        <v>12000</v>
-      </c>
-      <c r="I17" s="3">
-        <v>14700</v>
-      </c>
-      <c r="J17" s="3">
-        <v>13600</v>
-      </c>
-      <c r="K17" s="3">
-        <v>2200</v>
-      </c>
-      <c r="L17" s="3">
-        <v>4500</v>
-      </c>
-      <c r="M17" s="3">
-        <v>1600</v>
-      </c>
-      <c r="N17" s="3">
-        <v>2700</v>
-      </c>
-      <c r="O17" s="3">
-        <v>0</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
+      <c r="Q17" s="3">
+        <v>0</v>
       </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-1900</v>
+        <v>-1000</v>
       </c>
       <c r="E18" s="3">
-        <v>-2400</v>
+        <v>-1000</v>
       </c>
       <c r="F18" s="3">
-        <v>-2500</v>
+        <v>-1000</v>
       </c>
       <c r="G18" s="3">
-        <v>5000</v>
+        <v>-1000</v>
       </c>
       <c r="H18" s="3">
-        <v>1100</v>
+        <v>-1200</v>
       </c>
       <c r="I18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K18" s="3">
         <v>9800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>1400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>8900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>6300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>2700</v>
       </c>
-      <c r="O18" s="3">
-        <v>0</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
+      <c r="Q18" s="3">
+        <v>0</v>
       </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1244,131 +1309,145 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="L20" s="3">
+        <v>300</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
-        <v>600</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
-        <v>300</v>
-      </c>
-      <c r="J20" s="3">
-        <v>300</v>
-      </c>
-      <c r="K20" s="3">
-        <v>100</v>
-      </c>
-      <c r="L20" s="3">
-        <v>200</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-700</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-1100</v>
       </c>
       <c r="J21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
         <v>2000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>9300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>6400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>2700</v>
       </c>
-      <c r="O21" s="3">
-        <v>0</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
+      <c r="Q21" s="3">
+        <v>0</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1394,66 +1473,78 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-1500</v>
+        <v>-900</v>
       </c>
       <c r="E23" s="3">
-        <v>-2100</v>
+        <v>-900</v>
       </c>
       <c r="F23" s="3">
-        <v>-2400</v>
+        <v>-700</v>
       </c>
       <c r="G23" s="3">
-        <v>5600</v>
+        <v>-700</v>
       </c>
       <c r="H23" s="3">
-        <v>1400</v>
+        <v>-1100</v>
       </c>
       <c r="I23" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K23" s="3">
         <v>10100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>1700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>9100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>6300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>2600</v>
       </c>
-      <c r="O23" s="3">
-        <v>0</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
+      <c r="Q23" s="3">
+        <v>0</v>
       </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -1467,14 +1558,14 @@
       <c r="I24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="J24" s="3">
+        <v>0</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1485,17 +1576,23 @@
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1544,108 +1641,126 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-1500</v>
+        <v>-900</v>
       </c>
       <c r="E26" s="3">
-        <v>-2100</v>
+        <v>-900</v>
       </c>
       <c r="F26" s="3">
-        <v>-2400</v>
+        <v>-700</v>
       </c>
       <c r="G26" s="3">
-        <v>5600</v>
+        <v>-700</v>
       </c>
       <c r="H26" s="3">
-        <v>1400</v>
+        <v>-1100</v>
       </c>
       <c r="I26" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K26" s="3">
         <v>10100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>1700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>9100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>6300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>2600</v>
       </c>
-      <c r="O26" s="3">
-        <v>0</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
+      <c r="Q26" s="3">
+        <v>0</v>
       </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-1500</v>
+        <v>-900</v>
       </c>
       <c r="E27" s="3">
-        <v>-2100</v>
+        <v>-900</v>
       </c>
       <c r="F27" s="3">
-        <v>-2400</v>
+        <v>-700</v>
       </c>
       <c r="G27" s="3">
-        <v>5600</v>
+        <v>-700</v>
       </c>
       <c r="H27" s="3">
-        <v>1400</v>
+        <v>-1100</v>
       </c>
       <c r="I27" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K27" s="3">
         <v>10100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>1700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>9100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>6300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>2600</v>
       </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
+      <c r="Q27" s="3">
+        <v>0</v>
       </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1694,8 +1809,14 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1744,8 +1865,14 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1794,8 +1921,14 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1844,108 +1977,126 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-500</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>100</v>
+      </c>
+      <c r="G32" s="3">
+        <v>100</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="L32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>-600</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-1500</v>
+        <v>-900</v>
       </c>
       <c r="E33" s="3">
-        <v>-2100</v>
+        <v>-900</v>
       </c>
       <c r="F33" s="3">
-        <v>-2400</v>
+        <v>-700</v>
       </c>
       <c r="G33" s="3">
-        <v>5600</v>
+        <v>-700</v>
       </c>
       <c r="H33" s="3">
-        <v>1400</v>
+        <v>-1100</v>
       </c>
       <c r="I33" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K33" s="3">
         <v>10100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>1700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>9100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>6300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>2600</v>
       </c>
-      <c r="O33" s="3">
-        <v>0</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
+      <c r="Q33" s="3">
+        <v>0</v>
       </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1994,113 +2145,131 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-1500</v>
+        <v>-900</v>
       </c>
       <c r="E35" s="3">
-        <v>-2100</v>
+        <v>-900</v>
       </c>
       <c r="F35" s="3">
-        <v>-2400</v>
+        <v>-700</v>
       </c>
       <c r="G35" s="3">
-        <v>5600</v>
+        <v>-700</v>
       </c>
       <c r="H35" s="3">
-        <v>1400</v>
+        <v>-1100</v>
       </c>
       <c r="I35" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K35" s="3">
         <v>10100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>1700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>9100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>6300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>2600</v>
       </c>
-      <c r="O35" s="3">
-        <v>0</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
+      <c r="Q35" s="3">
+        <v>0</v>
       </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44377</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44196</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44012</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>43830</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43646</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43465</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43281</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2119,8 +2288,10 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2139,47 +2310,49 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>18800</v>
+      </c>
+      <c r="F41" s="3">
         <v>17700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
+        <v>17700</v>
+      </c>
+      <c r="H41" s="3">
         <v>21600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="I41" s="3">
+        <v>21600</v>
+      </c>
+      <c r="J41" s="3">
         <v>17200</v>
       </c>
-      <c r="G41" s="3">
-        <v>38700</v>
-      </c>
-      <c r="H41" s="3">
-        <v>29400</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>42600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>18200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>9200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>9200</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2189,44 +2362,50 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E42" s="3">
+        <v>6800</v>
+      </c>
+      <c r="F42" s="3">
         <v>3200</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
-        <v>1900</v>
+        <v>3200</v>
       </c>
       <c r="H42" s="3">
-        <v>3700</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>2400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>17500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>9800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>1700</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2239,47 +2418,53 @@
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="E43" s="3">
+        <v>800</v>
+      </c>
+      <c r="F43" s="3">
+        <v>300</v>
+      </c>
+      <c r="G43" s="3">
+        <v>300</v>
+      </c>
+      <c r="H43" s="3">
         <v>1200</v>
       </c>
-      <c r="F43" s="3">
-        <v>7900</v>
-      </c>
-      <c r="G43" s="3">
-        <v>5000</v>
-      </c>
-      <c r="H43" s="3">
-        <v>2400</v>
-      </c>
       <c r="I43" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J43" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K43" s="3">
         <v>2100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>300</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2289,31 +2474,37 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2339,47 +2530,53 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>16500</v>
+        <v>1800</v>
       </c>
       <c r="E45" s="3">
-        <v>16100</v>
+        <v>1800</v>
       </c>
       <c r="F45" s="3">
-        <v>17100</v>
+        <v>1800</v>
       </c>
       <c r="G45" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J45" s="3">
+        <v>9000</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
+        <v>2900</v>
+      </c>
+      <c r="M45" s="3">
         <v>600</v>
       </c>
-      <c r="H45" s="3">
-        <v>600</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3">
-        <v>2900</v>
-      </c>
-      <c r="K45" s="3">
-        <v>600</v>
-      </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2389,47 +2586,53 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>43700</v>
+      </c>
+      <c r="F46" s="3">
         <v>37900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
+        <v>37900</v>
+      </c>
+      <c r="H46" s="3">
         <v>38900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
+        <v>38900</v>
+      </c>
+      <c r="J46" s="3">
         <v>42200</v>
       </c>
-      <c r="G46" s="3">
-        <v>46200</v>
-      </c>
-      <c r="H46" s="3">
-        <v>36100</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>47200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>39000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>11800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>12200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>9500</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2439,8 +2642,14 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2454,16 +2663,16 @@
         <v>900</v>
       </c>
       <c r="G47" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="H47" s="3">
-        <v>3700</v>
+        <v>900</v>
       </c>
       <c r="I47" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="J47" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="K47" s="3">
         <v>500</v>
@@ -2474,11 +2683,11 @@
       <c r="M47" s="3">
         <v>500</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
+      <c r="N47" s="3">
+        <v>500</v>
+      </c>
+      <c r="O47" s="3">
+        <v>500</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
@@ -2489,47 +2698,53 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F48" s="3">
         <v>9200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
+        <v>9200</v>
+      </c>
+      <c r="H48" s="3">
         <v>9100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="I48" s="3">
+        <v>9100</v>
+      </c>
+      <c r="J48" s="3">
         <v>9500</v>
       </c>
-      <c r="G48" s="3">
-        <v>9600</v>
-      </c>
-      <c r="H48" s="3">
-        <v>9900</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>500</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2539,47 +2754,53 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>100</v>
+      </c>
+      <c r="F49" s="3">
         <v>500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
+        <v>500</v>
+      </c>
+      <c r="H49" s="3">
         <v>700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="I49" s="3">
+        <v>700</v>
+      </c>
+      <c r="J49" s="3">
         <v>800</v>
       </c>
-      <c r="G49" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H49" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>800</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2589,8 +2810,14 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2639,8 +2866,14 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2689,47 +2922,53 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
         <v>100</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="E52" s="3">
+        <v>100</v>
+      </c>
+      <c r="F52" s="3">
+        <v>100</v>
+      </c>
+      <c r="G52" s="3">
+        <v>100</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K52" s="3">
         <v>1500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>700</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2739,8 +2978,14 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2789,47 +3034,53 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>53800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>53800</v>
+      </c>
+      <c r="F54" s="3">
         <v>48600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
+        <v>48600</v>
+      </c>
+      <c r="H54" s="3">
         <v>49500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
+        <v>49500</v>
+      </c>
+      <c r="J54" s="3">
         <v>53400</v>
       </c>
-      <c r="G54" s="3">
-        <v>57700</v>
-      </c>
-      <c r="H54" s="3">
-        <v>50800</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>50500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>41100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>14400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>14700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>12000</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2839,8 +3090,14 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2859,8 +3116,10 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2879,47 +3138,49 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F57" s="3">
         <v>2600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H57" s="3">
         <v>2400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="I57" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J57" s="3">
         <v>3000</v>
       </c>
-      <c r="G57" s="3">
-        <v>3700</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>3200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>6100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>300</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2929,8 +3190,14 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2979,8 +3246,14 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2988,38 +3261,38 @@
         <v>500</v>
       </c>
       <c r="E59" s="3">
+        <v>500</v>
+      </c>
+      <c r="F59" s="3">
+        <v>400</v>
+      </c>
+      <c r="G59" s="3">
+        <v>400</v>
+      </c>
+      <c r="H59" s="3">
         <v>600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="I59" s="3">
+        <v>600</v>
+      </c>
+      <c r="J59" s="3">
+        <v>600</v>
+      </c>
+      <c r="K59" s="3">
+        <v>3700</v>
+      </c>
+      <c r="L59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M59" s="3">
         <v>800</v>
       </c>
-      <c r="G59" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H59" s="3">
-        <v>2000</v>
-      </c>
-      <c r="I59" s="3">
-        <v>3700</v>
-      </c>
-      <c r="J59" s="3">
-        <v>1500</v>
-      </c>
-      <c r="K59" s="3">
-        <v>800</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1400</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3029,47 +3302,53 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F60" s="3">
         <v>3100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
+        <v>3100</v>
+      </c>
+      <c r="H60" s="3">
         <v>3000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="I60" s="3">
+        <v>3000</v>
+      </c>
+      <c r="J60" s="3">
         <v>3800</v>
       </c>
-      <c r="G60" s="3">
-        <v>5000</v>
-      </c>
-      <c r="H60" s="3">
-        <v>3600</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>7500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1700</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3079,8 +3358,14 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3129,22 +3414,28 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -3164,11 +3455,11 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -3179,8 +3470,14 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3229,8 +3526,14 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3279,8 +3582,14 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3329,47 +3638,53 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F66" s="3">
         <v>3100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
+        <v>3100</v>
+      </c>
+      <c r="H66" s="3">
         <v>3000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="I66" s="3">
+        <v>3000</v>
+      </c>
+      <c r="J66" s="3">
         <v>3800</v>
       </c>
-      <c r="G66" s="3">
-        <v>5000</v>
-      </c>
-      <c r="H66" s="3">
-        <v>3600</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>6900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>7500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1700</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3379,8 +3694,14 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3399,8 +3720,10 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3449,8 +3772,14 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3499,8 +3828,14 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3549,8 +3884,14 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3599,47 +3940,53 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>23000</v>
+      </c>
+      <c r="F72" s="3">
         <v>24800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
+        <v>24800</v>
+      </c>
+      <c r="H72" s="3">
         <v>26300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="I72" s="3">
+        <v>26300</v>
+      </c>
+      <c r="J72" s="3">
         <v>28400</v>
       </c>
-      <c r="G72" s="3">
-        <v>30800</v>
-      </c>
-      <c r="H72" s="3">
-        <v>25200</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>23800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>13800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>12100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>11700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>8900</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3649,8 +3996,14 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3699,8 +4052,14 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3749,8 +4108,14 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3799,47 +4164,53 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>51100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>51100</v>
+      </c>
+      <c r="F76" s="3">
         <v>45500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
+        <v>45500</v>
+      </c>
+      <c r="H76" s="3">
         <v>46500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
+        <v>46500</v>
+      </c>
+      <c r="J76" s="3">
         <v>49600</v>
       </c>
-      <c r="G76" s="3">
-        <v>52600</v>
-      </c>
-      <c r="H76" s="3">
-        <v>47200</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>43600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>33600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>13300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>13100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>10300</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3849,8 +4220,14 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3899,113 +4276,131 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44377</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44196</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44012</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>43830</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43646</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43465</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43281</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-1500</v>
+        <v>-900</v>
       </c>
       <c r="E81" s="3">
-        <v>-2100</v>
+        <v>-900</v>
       </c>
       <c r="F81" s="3">
-        <v>-2400</v>
+        <v>-700</v>
       </c>
       <c r="G81" s="3">
-        <v>5600</v>
+        <v>-700</v>
       </c>
       <c r="H81" s="3">
-        <v>1400</v>
+        <v>-1100</v>
       </c>
       <c r="I81" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K81" s="3">
         <v>10100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>1700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>9100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>6300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>2600</v>
       </c>
-      <c r="O81" s="3">
-        <v>0</v>
-      </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
+      <c r="Q81" s="3">
+        <v>0</v>
       </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4024,37 +4419,39 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
@@ -4074,8 +4471,14 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4124,8 +4527,14 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4174,8 +4583,14 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4224,8 +4639,14 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4274,8 +4695,14 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4324,37 +4751,43 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3">
+        <v>0</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
@@ -4374,8 +4807,14 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4394,31 +4833,33 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -4426,11 +4867,11 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
@@ -4444,8 +4885,14 @@
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4494,8 +4941,14 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4544,37 +4997,43 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
@@ -4594,8 +5053,14 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4614,31 +5079,33 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4664,8 +5131,14 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4714,8 +5187,14 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4764,8 +5243,14 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4814,37 +5299,43 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
@@ -4864,37 +5355,43 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
@@ -4914,8 +5411,14 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4940,11 +5443,11 @@
       <c r="J102" s="3">
         <v>0</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
@@ -4962,6 +5465,12 @@
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OCG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OCG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="92">
   <si>
     <t>OCG</t>
   </si>
@@ -656,110 +656,117 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44196</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44012</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43830</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43646</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43465</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43281</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3">
+        <v>100</v>
+      </c>
+      <c r="F8" s="3">
         <v>200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>200</v>
-      </c>
-      <c r="F8" s="3">
-        <v>400</v>
-      </c>
-      <c r="G8" s="3">
-        <v>400</v>
       </c>
       <c r="H8" s="3">
         <v>400</v>
@@ -771,45 +778,51 @@
         <v>400</v>
       </c>
       <c r="K8" s="3">
+        <v>400</v>
+      </c>
+      <c r="L8" s="3">
+        <v>400</v>
+      </c>
+      <c r="M8" s="3">
         <v>24500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>15000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>2500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>13400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>7900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>5400</v>
       </c>
-      <c r="Q8" s="3">
-        <v>0</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
+      <c r="S8" s="3">
+        <v>0</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F9" s="3">
         <v>100</v>
@@ -824,40 +837,46 @@
         <v>100</v>
       </c>
       <c r="J9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9" s="3">
+        <v>100</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3">
         <v>1400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>2200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>1300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>500</v>
       </c>
-      <c r="Q9" s="3">
-        <v>0</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
+      <c r="S9" s="3">
+        <v>0</v>
       </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -868,10 +887,10 @@
         <v>100</v>
       </c>
       <c r="F10" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="G10" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H10" s="3">
         <v>300</v>
@@ -880,40 +899,46 @@
         <v>300</v>
       </c>
       <c r="J10" s="3">
+        <v>300</v>
+      </c>
+      <c r="K10" s="3">
+        <v>300</v>
+      </c>
+      <c r="L10" s="3">
         <v>400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>23100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>12800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>2100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>12100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>7300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>4900</v>
       </c>
-      <c r="Q10" s="3">
-        <v>0</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
+      <c r="S10" s="3">
+        <v>0</v>
       </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -934,8 +959,10 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -990,8 +1017,14 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1046,23 +1079,29 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
@@ -1070,14 +1109,14 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-100</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1102,13 +1141,19 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
         <v>200</v>
@@ -1120,20 +1165,20 @@
         <v>200</v>
       </c>
       <c r="H15" s="3">
+        <v>200</v>
+      </c>
+      <c r="I15" s="3">
+        <v>200</v>
+      </c>
+      <c r="J15" s="3">
         <v>100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>200</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1158,8 +1203,14 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1177,72 +1228,80 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>600</v>
+      </c>
+      <c r="E17" s="3">
+        <v>600</v>
+      </c>
+      <c r="F17" s="3">
         <v>1300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1400</v>
-      </c>
-      <c r="H17" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I17" s="3">
-        <v>1600</v>
       </c>
       <c r="J17" s="3">
         <v>1600</v>
       </c>
       <c r="K17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="M17" s="3">
         <v>14700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>13600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>4500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2700</v>
       </c>
-      <c r="Q17" s="3">
-        <v>0</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
+      <c r="S17" s="3">
+        <v>0</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
       <c r="E18" s="3">
-        <v>-1000</v>
+        <v>-600</v>
       </c>
       <c r="F18" s="3">
         <v>-1000</v>
@@ -1251,46 +1310,52 @@
         <v>-1000</v>
       </c>
       <c r="H18" s="3">
-        <v>-1200</v>
+        <v>-1000</v>
       </c>
       <c r="I18" s="3">
-        <v>-1200</v>
+        <v>-1000</v>
       </c>
       <c r="J18" s="3">
         <v>-1200</v>
       </c>
       <c r="K18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="M18" s="3">
         <v>9800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>1400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>8900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>6300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>2700</v>
       </c>
-      <c r="Q18" s="3">
-        <v>0</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
+      <c r="S18" s="3">
+        <v>0</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1311,120 +1376,134 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
+      <c r="S20" s="3">
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-700</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-1100</v>
       </c>
       <c r="J21" s="3">
         <v>-1100</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
+      <c r="K21" s="3">
+        <v>-1100</v>
       </c>
       <c r="L21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>2000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>9300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>6400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>2700</v>
       </c>
-      <c r="Q21" s="3">
-        <v>0</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
+      <c r="S21" s="3">
+        <v>0</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1449,11 +1528,11 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1479,78 +1558,90 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F23" s="3">
         <v>-900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-1100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>10100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>1700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>9100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>6300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>2600</v>
       </c>
-      <c r="Q23" s="3">
-        <v>0</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
+      <c r="S23" s="3">
+        <v>0</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H24" s="3">
         <v>0</v>
@@ -1564,14 +1655,14 @@
       <c r="K24" s="3">
         <v>0</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
+      <c r="L24" s="3">
+        <v>0</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
@@ -1582,17 +1673,23 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1647,120 +1744,138 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F26" s="3">
         <v>-900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-1100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>10100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>9100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>6300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>2600</v>
       </c>
-      <c r="Q26" s="3">
-        <v>0</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
+      <c r="S26" s="3">
+        <v>0</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>10100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>9100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>6300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>2600</v>
       </c>
-      <c r="Q27" s="3">
-        <v>0</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
+      <c r="S27" s="3">
+        <v>0</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1815,8 +1930,14 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1871,8 +1992,14 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1927,8 +2054,14 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1983,120 +2116,138 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
+      <c r="S32" s="3">
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>10100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>9100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>6300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>2600</v>
       </c>
-      <c r="Q33" s="3">
-        <v>0</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
+      <c r="S33" s="3">
+        <v>0</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2151,125 +2302,143 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>10100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>9100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>6300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>2600</v>
       </c>
-      <c r="Q35" s="3">
-        <v>0</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
+      <c r="S35" s="3">
+        <v>0</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44196</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44012</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43830</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43646</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43465</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43281</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2290,8 +2459,10 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2312,53 +2483,55 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>17100</v>
+      </c>
+      <c r="F41" s="3">
         <v>18800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>18800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>17700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>17700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>21600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>21600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>17200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>42600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>18200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>9200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>9200</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2368,50 +2541,56 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E42" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F42" s="3">
         <v>6800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>6800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>3200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>3200</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>2400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>17500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>9800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>1700</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2424,53 +2603,59 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F43" s="3">
         <v>800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>3500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>300</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2480,16 +2665,22 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>3</v>
+      <c r="D44" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1200</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>3</v>
@@ -2506,11 +2697,11 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2536,16 +2727,22 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1800</v>
+        <v>10800</v>
       </c>
       <c r="E45" s="3">
-        <v>1800</v>
+        <v>10800</v>
       </c>
       <c r="F45" s="3">
         <v>1800</v>
@@ -2554,35 +2751,35 @@
         <v>1800</v>
       </c>
       <c r="H45" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I45" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J45" s="3">
         <v>1700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>9000</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>2900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>600</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3">
         <v>100</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2592,53 +2789,59 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>41900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>41900</v>
+      </c>
+      <c r="F46" s="3">
         <v>43700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>43700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>37900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>37900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>38900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>38900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>42200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>47200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>39000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>11800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>12200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>9500</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2648,8 +2851,14 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2675,10 +2884,10 @@
         <v>900</v>
       </c>
       <c r="K47" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="L47" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="M47" s="3">
         <v>500</v>
@@ -2689,11 +2898,11 @@
       <c r="O47" s="3">
         <v>500</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
+      <c r="P47" s="3">
+        <v>500</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>500</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
@@ -2704,53 +2913,59 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>8600</v>
+      </c>
+      <c r="F48" s="3">
         <v>9000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>9000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>9200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>9200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>9100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>9100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>9500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>500</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2760,53 +2975,59 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F49" s="3">
         <v>100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>800</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2816,8 +3037,14 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2872,8 +3099,14 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,16 +3161,22 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>100</v>
-      </c>
-      <c r="E52" s="3">
-        <v>100</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F52" s="3">
         <v>100</v>
@@ -2945,36 +3184,36 @@
       <c r="G52" s="3">
         <v>100</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
+      <c r="H52" s="3">
+        <v>100</v>
+      </c>
+      <c r="I52" s="3">
+        <v>100</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3">
         <v>1500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>700</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2984,8 +3223,14 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3040,53 +3285,59 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>53000</v>
+      </c>
+      <c r="F54" s="3">
         <v>53800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>53800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>48600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>48600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>49500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>49500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>53400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>50500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>41100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>14400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>14700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>12000</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3096,8 +3347,14 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3118,8 +3375,10 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3140,53 +3399,55 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F57" s="3">
         <v>2200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>2400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>3000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>6100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>300</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3196,8 +3457,14 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3252,53 +3519,59 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>700</v>
+      </c>
+      <c r="F59" s="3">
         <v>500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>400</v>
-      </c>
-      <c r="H59" s="3">
-        <v>600</v>
-      </c>
-      <c r="I59" s="3">
-        <v>600</v>
       </c>
       <c r="J59" s="3">
         <v>600</v>
       </c>
       <c r="K59" s="3">
+        <v>600</v>
+      </c>
+      <c r="L59" s="3">
+        <v>600</v>
+      </c>
+      <c r="M59" s="3">
         <v>3700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1400</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3308,53 +3581,59 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F60" s="3">
         <v>2700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>6900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>7500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1700</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3364,8 +3643,14 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3420,8 +3705,14 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3461,11 +3752,11 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
@@ -3476,8 +3767,14 @@
       <c r="T62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3532,8 +3829,14 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3588,8 +3891,14 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3644,53 +3953,59 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F66" s="3">
         <v>2700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>3100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>3100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>6900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>7500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1700</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3700,8 +4015,14 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3722,8 +4043,10 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3778,8 +4101,14 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3834,8 +4163,14 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3890,8 +4225,14 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3946,53 +4287,59 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>22400</v>
+      </c>
+      <c r="F72" s="3">
         <v>23000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>23000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>24800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>24800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>26300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>26300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>28400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>23800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>13800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>12100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>11700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>8900</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4002,8 +4349,14 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4058,8 +4411,14 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4114,8 +4473,14 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4170,53 +4535,59 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>49900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>49900</v>
+      </c>
+      <c r="F76" s="3">
         <v>51100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>51100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>45500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>45500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>46500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>46500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>49600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>43600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>33600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>13300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>13100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>10300</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4226,8 +4597,14 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4282,125 +4659,143 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44196</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44012</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43830</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43646</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43465</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43281</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>10100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>9100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>6300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>2600</v>
       </c>
-      <c r="Q81" s="3">
-        <v>0</v>
-      </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
+      <c r="S81" s="3">
+        <v>0</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4421,8 +4816,10 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4447,17 +4844,17 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
@@ -4477,8 +4874,14 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4533,8 +4936,14 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4589,8 +4998,14 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4645,8 +5060,14 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4701,8 +5122,14 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4757,8 +5184,14 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4783,17 +5216,17 @@
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3">
+        <v>0</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
@@ -4813,8 +5246,14 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4835,8 +5274,10 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4861,11 +5302,11 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -4873,11 +5314,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
@@ -4891,8 +5332,14 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4947,8 +5394,14 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5003,8 +5456,14 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5029,17 +5488,17 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
@@ -5059,8 +5518,14 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5081,8 +5546,10 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5107,11 +5574,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5137,8 +5604,14 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5193,8 +5666,14 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5249,8 +5728,14 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5305,8 +5790,14 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5331,17 +5822,17 @@
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
@@ -5361,8 +5852,14 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5387,17 +5884,17 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
@@ -5417,31 +5914,37 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>0</v>
-      </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
-        <v>0</v>
+      <c r="D102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
@@ -5449,11 +5952,11 @@
       <c r="L102" s="3">
         <v>0</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
@@ -5471,6 +5974,12 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/OCG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OCG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="92">
   <si>
     <t>OCG</t>
   </si>
@@ -762,11 +762,11 @@
       <c r="E8" s="3">
         <v>100</v>
       </c>
-      <c r="F8" s="3">
-        <v>200</v>
-      </c>
-      <c r="G8" s="3">
-        <v>200</v>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H8" s="3">
         <v>400</v>
@@ -774,8 +774,8 @@
       <c r="I8" s="3">
         <v>400</v>
       </c>
-      <c r="J8" s="3">
-        <v>400</v>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>400</v>
@@ -824,11 +824,11 @@
       <c r="E9" s="3">
         <v>0</v>
       </c>
-      <c r="F9" s="3">
-        <v>100</v>
-      </c>
-      <c r="G9" s="3">
-        <v>100</v>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H9" s="3">
         <v>100</v>
@@ -836,8 +836,8 @@
       <c r="I9" s="3">
         <v>100</v>
       </c>
-      <c r="J9" s="3">
-        <v>100</v>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K9" s="3">
         <v>100</v>
@@ -886,11 +886,11 @@
       <c r="E10" s="3">
         <v>100</v>
       </c>
-      <c r="F10" s="3">
-        <v>100</v>
-      </c>
-      <c r="G10" s="3">
-        <v>100</v>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H10" s="3">
         <v>300</v>
@@ -898,8 +898,8 @@
       <c r="I10" s="3">
         <v>300</v>
       </c>
-      <c r="J10" s="3">
-        <v>300</v>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K10" s="3">
         <v>300</v>
@@ -1096,11 +1096,11 @@
       <c r="E14" s="3">
         <v>0</v>
       </c>
-      <c r="F14" s="3">
-        <v>100</v>
-      </c>
-      <c r="G14" s="3">
-        <v>100</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
@@ -1108,8 +1108,8 @@
       <c r="I14" s="3">
         <v>0</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1159,10 +1159,10 @@
         <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3">
         <v>200</v>
@@ -1171,7 +1171,7 @@
         <v>200</v>
       </c>
       <c r="J15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>100</v>
@@ -1241,11 +1241,11 @@
       <c r="E17" s="3">
         <v>600</v>
       </c>
-      <c r="F17" s="3">
-        <v>1300</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1300</v>
+      <c r="F17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H17" s="3">
         <v>1400</v>
@@ -1253,8 +1253,8 @@
       <c r="I17" s="3">
         <v>1400</v>
       </c>
-      <c r="J17" s="3">
-        <v>1600</v>
+      <c r="J17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K17" s="3">
         <v>1600</v>
@@ -1303,11 +1303,11 @@
       <c r="E18" s="3">
         <v>-600</v>
       </c>
-      <c r="F18" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-1000</v>
+      <c r="F18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H18" s="3">
         <v>-1000</v>
@@ -1315,8 +1315,8 @@
       <c r="I18" s="3">
         <v>-1000</v>
       </c>
-      <c r="J18" s="3">
-        <v>-1200</v>
+      <c r="J18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K18" s="3">
         <v>-1200</v>
@@ -1389,11 +1389,11 @@
       <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H20" s="3">
         <v>-100</v>
@@ -1401,8 +1401,8 @@
       <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1452,10 +1452,10 @@
         <v>-300</v>
       </c>
       <c r="F21" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
         <v>-700</v>
@@ -1464,7 +1464,7 @@
         <v>-700</v>
       </c>
       <c r="J21" s="3">
-        <v>-1100</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3">
         <v>-1100</v>
@@ -1575,11 +1575,11 @@
       <c r="E23" s="3">
         <v>-300</v>
       </c>
-      <c r="F23" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-900</v>
+      <c r="F23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H23" s="3">
         <v>-700</v>
@@ -1587,8 +1587,8 @@
       <c r="I23" s="3">
         <v>-700</v>
       </c>
-      <c r="J23" s="3">
-        <v>-1100</v>
+      <c r="J23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K23" s="3">
         <v>-1100</v>
@@ -1649,8 +1649,8 @@
       <c r="I24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1761,11 +1761,11 @@
       <c r="E26" s="3">
         <v>-300</v>
       </c>
-      <c r="F26" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-900</v>
+      <c r="F26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H26" s="3">
         <v>-700</v>
@@ -1773,8 +1773,8 @@
       <c r="I26" s="3">
         <v>-700</v>
       </c>
-      <c r="J26" s="3">
-        <v>-1100</v>
+      <c r="J26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K26" s="3">
         <v>-1100</v>
@@ -1823,11 +1823,11 @@
       <c r="E27" s="3">
         <v>-300</v>
       </c>
-      <c r="F27" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-900</v>
+      <c r="F27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H27" s="3">
         <v>-700</v>
@@ -1835,8 +1835,8 @@
       <c r="I27" s="3">
         <v>-700</v>
       </c>
-      <c r="J27" s="3">
-        <v>-1100</v>
+      <c r="J27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K27" s="3">
         <v>-1100</v>
@@ -2133,11 +2133,11 @@
       <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H32" s="3">
         <v>100</v>
@@ -2145,8 +2145,8 @@
       <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2195,11 +2195,11 @@
       <c r="E33" s="3">
         <v>-300</v>
       </c>
-      <c r="F33" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-900</v>
+      <c r="F33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H33" s="3">
         <v>-700</v>
@@ -2207,8 +2207,8 @@
       <c r="I33" s="3">
         <v>-700</v>
       </c>
-      <c r="J33" s="3">
-        <v>-1100</v>
+      <c r="J33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K33" s="3">
         <v>-1100</v>
@@ -2319,11 +2319,11 @@
       <c r="E35" s="3">
         <v>-300</v>
       </c>
-      <c r="F35" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-900</v>
+      <c r="F35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H35" s="3">
         <v>-700</v>
@@ -2331,8 +2331,8 @@
       <c r="I35" s="3">
         <v>-700</v>
       </c>
-      <c r="J35" s="3">
-        <v>-1100</v>
+      <c r="J35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K35" s="3">
         <v>-1100</v>
@@ -2496,11 +2496,11 @@
       <c r="E41" s="3">
         <v>17100</v>
       </c>
-      <c r="F41" s="3">
-        <v>18800</v>
-      </c>
-      <c r="G41" s="3">
-        <v>18800</v>
+      <c r="F41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H41" s="3">
         <v>17700</v>
@@ -2508,8 +2508,8 @@
       <c r="I41" s="3">
         <v>17700</v>
       </c>
-      <c r="J41" s="3">
-        <v>21600</v>
+      <c r="J41" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K41" s="3">
         <v>21600</v>
@@ -2559,10 +2559,10 @@
         <v>5300</v>
       </c>
       <c r="F42" s="3">
-        <v>6800</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>6800</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
         <v>3200</v>
@@ -2615,16 +2615,16 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="E43" s="3">
-        <v>1100</v>
-      </c>
-      <c r="F43" s="3">
-        <v>800</v>
-      </c>
-      <c r="G43" s="3">
-        <v>800</v>
+        <v>0</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H43" s="3">
         <v>300</v>
@@ -2632,8 +2632,8 @@
       <c r="I43" s="3">
         <v>300</v>
       </c>
-      <c r="J43" s="3">
-        <v>1200</v>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>1200</v>
@@ -2739,25 +2739,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>10800</v>
+        <v>11800</v>
       </c>
       <c r="E45" s="3">
-        <v>10800</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1800</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1800</v>
+        <v>11800</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H45" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="I45" s="3">
-        <v>1800</v>
-      </c>
-      <c r="J45" s="3">
-        <v>1700</v>
+        <v>1900</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K45" s="3">
         <v>1700</v>
@@ -2806,11 +2806,11 @@
       <c r="E46" s="3">
         <v>41900</v>
       </c>
-      <c r="F46" s="3">
-        <v>43700</v>
-      </c>
-      <c r="G46" s="3">
-        <v>43700</v>
+      <c r="F46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H46" s="3">
         <v>37900</v>
@@ -2818,8 +2818,8 @@
       <c r="I46" s="3">
         <v>37900</v>
       </c>
-      <c r="J46" s="3">
-        <v>38900</v>
+      <c r="J46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K46" s="3">
         <v>38900</v>
@@ -2868,11 +2868,11 @@
       <c r="E47" s="3">
         <v>900</v>
       </c>
-      <c r="F47" s="3">
-        <v>900</v>
-      </c>
-      <c r="G47" s="3">
-        <v>900</v>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H47" s="3">
         <v>900</v>
@@ -2880,8 +2880,8 @@
       <c r="I47" s="3">
         <v>900</v>
       </c>
-      <c r="J47" s="3">
-        <v>900</v>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>900</v>
@@ -2930,11 +2930,11 @@
       <c r="E48" s="3">
         <v>8600</v>
       </c>
-      <c r="F48" s="3">
-        <v>9000</v>
-      </c>
-      <c r="G48" s="3">
-        <v>9000</v>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H48" s="3">
         <v>9200</v>
@@ -2942,8 +2942,8 @@
       <c r="I48" s="3">
         <v>9200</v>
       </c>
-      <c r="J48" s="3">
-        <v>9100</v>
+      <c r="J48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K48" s="3">
         <v>9100</v>
@@ -2992,11 +2992,11 @@
       <c r="E49" s="3">
         <v>1500</v>
       </c>
-      <c r="F49" s="3">
-        <v>100</v>
-      </c>
-      <c r="G49" s="3">
-        <v>100</v>
+      <c r="F49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H49" s="3">
         <v>500</v>
@@ -3004,8 +3004,8 @@
       <c r="I49" s="3">
         <v>500</v>
       </c>
-      <c r="J49" s="3">
-        <v>700</v>
+      <c r="J49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K49" s="3">
         <v>700</v>
@@ -3178,11 +3178,11 @@
       <c r="E52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F52" s="3">
-        <v>100</v>
-      </c>
-      <c r="G52" s="3">
-        <v>100</v>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
@@ -3302,11 +3302,11 @@
       <c r="E54" s="3">
         <v>53000</v>
       </c>
-      <c r="F54" s="3">
-        <v>53800</v>
-      </c>
-      <c r="G54" s="3">
-        <v>53800</v>
+      <c r="F54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H54" s="3">
         <v>48600</v>
@@ -3314,8 +3314,8 @@
       <c r="I54" s="3">
         <v>48600</v>
       </c>
-      <c r="J54" s="3">
-        <v>49500</v>
+      <c r="J54" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K54" s="3">
         <v>49500</v>
@@ -3412,11 +3412,11 @@
       <c r="E57" s="3">
         <v>2400</v>
       </c>
-      <c r="F57" s="3">
-        <v>2200</v>
-      </c>
-      <c r="G57" s="3">
-        <v>2200</v>
+      <c r="F57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H57" s="3">
         <v>2600</v>
@@ -3424,8 +3424,8 @@
       <c r="I57" s="3">
         <v>2600</v>
       </c>
-      <c r="J57" s="3">
-        <v>2400</v>
+      <c r="J57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K57" s="3">
         <v>2400</v>
@@ -3474,11 +3474,11 @@
       <c r="E58" s="3">
         <v>0</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
+      <c r="F58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -3486,8 +3486,8 @@
       <c r="I58" s="3">
         <v>0</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
+      <c r="J58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3531,16 +3531,16 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E59" s="3">
-        <v>700</v>
-      </c>
-      <c r="F59" s="3">
-        <v>500</v>
-      </c>
-      <c r="G59" s="3">
-        <v>500</v>
+        <v>600</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H59" s="3">
         <v>400</v>
@@ -3548,8 +3548,8 @@
       <c r="I59" s="3">
         <v>400</v>
       </c>
-      <c r="J59" s="3">
-        <v>600</v>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K59" s="3">
         <v>600</v>
@@ -3598,11 +3598,11 @@
       <c r="E60" s="3">
         <v>3100</v>
       </c>
-      <c r="F60" s="3">
-        <v>2700</v>
-      </c>
-      <c r="G60" s="3">
-        <v>2700</v>
+      <c r="F60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H60" s="3">
         <v>3100</v>
@@ -3610,8 +3610,8 @@
       <c r="I60" s="3">
         <v>3100</v>
       </c>
-      <c r="J60" s="3">
-        <v>3000</v>
+      <c r="J60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K60" s="3">
         <v>3000</v>
@@ -3970,11 +3970,11 @@
       <c r="E66" s="3">
         <v>3100</v>
       </c>
-      <c r="F66" s="3">
-        <v>2700</v>
-      </c>
-      <c r="G66" s="3">
-        <v>2700</v>
+      <c r="F66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H66" s="3">
         <v>3100</v>
@@ -3982,8 +3982,8 @@
       <c r="I66" s="3">
         <v>3100</v>
       </c>
-      <c r="J66" s="3">
-        <v>3000</v>
+      <c r="J66" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K66" s="3">
         <v>3000</v>
@@ -4304,11 +4304,11 @@
       <c r="E72" s="3">
         <v>22400</v>
       </c>
-      <c r="F72" s="3">
-        <v>23000</v>
-      </c>
-      <c r="G72" s="3">
-        <v>23000</v>
+      <c r="F72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H72" s="3">
         <v>24800</v>
@@ -4316,8 +4316,8 @@
       <c r="I72" s="3">
         <v>24800</v>
       </c>
-      <c r="J72" s="3">
-        <v>26300</v>
+      <c r="J72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K72" s="3">
         <v>26300</v>
@@ -4552,11 +4552,11 @@
       <c r="E76" s="3">
         <v>49900</v>
       </c>
-      <c r="F76" s="3">
-        <v>51100</v>
-      </c>
-      <c r="G76" s="3">
-        <v>51100</v>
+      <c r="F76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H76" s="3">
         <v>45500</v>
@@ -4564,8 +4564,8 @@
       <c r="I76" s="3">
         <v>45500</v>
       </c>
-      <c r="J76" s="3">
-        <v>46500</v>
+      <c r="J76" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K76" s="3">
         <v>46500</v>
@@ -4743,11 +4743,11 @@
       <c r="E81" s="3">
         <v>-300</v>
       </c>
-      <c r="F81" s="3">
-        <v>-900</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-900</v>
+      <c r="F81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H81" s="3">
         <v>-700</v>
@@ -4755,8 +4755,8 @@
       <c r="I81" s="3">
         <v>-700</v>
       </c>
-      <c r="J81" s="3">
-        <v>-1100</v>
+      <c r="J81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K81" s="3">
         <v>-1100</v>

--- a/AAII_Financials/Quarterly/OCG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/OCG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="92">
   <si>
     <t>OCG</t>
   </si>
@@ -656,113 +656,119 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44012</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43830</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43646</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43465</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43281</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
+      <c r="D8" s="3">
+        <v>900</v>
       </c>
       <c r="E8" s="3">
+        <v>900</v>
+      </c>
+      <c r="F8" s="3">
         <v>100</v>
       </c>
-      <c r="F8" s="3">
-        <v>400</v>
-      </c>
       <c r="G8" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="H8" s="3">
         <v>400</v>
@@ -771,170 +777,188 @@
         <v>400</v>
       </c>
       <c r="J8" s="3">
-        <v>6600</v>
+        <v>400</v>
       </c>
       <c r="K8" s="3">
         <v>400</v>
       </c>
       <c r="L8" s="3">
+        <v>6600</v>
+      </c>
+      <c r="M8" s="3">
         <v>400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
+        <v>400</v>
+      </c>
+      <c r="O8" s="3">
         <v>24500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>15000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>2500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>13400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>7900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>5400</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
+      <c r="U8" s="3">
+        <v>0</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9" s="3">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
         <v>100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>100</v>
       </c>
-      <c r="H9" s="3">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
       <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3">
         <v>500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>100</v>
       </c>
-      <c r="L9" s="3">
-        <v>0</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3">
         <v>1400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>2200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>500</v>
       </c>
-      <c r="S9" s="3">
-        <v>0</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
+      <c r="U9" s="3">
+        <v>0</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>700</v>
+      </c>
+      <c r="F10" s="3">
         <v>100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>6100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>23100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>12800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>2100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>12100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>7300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>4900</v>
       </c>
-      <c r="S10" s="3">
-        <v>0</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
+      <c r="U10" s="3">
+        <v>0</v>
       </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -957,8 +981,10 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1019,8 +1045,14 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1081,16 +1113,22 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -1099,16 +1137,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3">
         <v>-100</v>
       </c>
       <c r="K14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L14" s="3">
         <v>-100</v>
@@ -1117,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1143,8 +1181,14 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1152,10 +1196,10 @@
         <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
         <v>200</v>
@@ -1164,23 +1208,23 @@
         <v>200</v>
       </c>
       <c r="I15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J15" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K15" s="3">
         <v>100</v>
       </c>
       <c r="L15" s="3">
+        <v>100</v>
+      </c>
+      <c r="M15" s="3">
+        <v>100</v>
+      </c>
+      <c r="N15" s="3">
         <v>200</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
@@ -1205,8 +1249,14 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1226,132 +1276,146 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>500</v>
+      </c>
+      <c r="F17" s="3">
         <v>600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1600</v>
-      </c>
-      <c r="I17" s="3">
-        <v>1600</v>
-      </c>
-      <c r="J17" s="3">
-        <v>6000</v>
       </c>
       <c r="K17" s="3">
         <v>1600</v>
       </c>
       <c r="L17" s="3">
+        <v>6000</v>
+      </c>
+      <c r="M17" s="3">
         <v>1600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O17" s="3">
         <v>14700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>13600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>2200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>4500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>1600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>2700</v>
       </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
+      <c r="U17" s="3">
+        <v>0</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-1000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-1200</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="J18" s="3">
-        <v>600</v>
       </c>
       <c r="K18" s="3">
         <v>-1200</v>
       </c>
       <c r="L18" s="3">
+        <v>600</v>
+      </c>
+      <c r="M18" s="3">
         <v>-1200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="O18" s="3">
         <v>9800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>8900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>6300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>2700</v>
       </c>
-      <c r="S18" s="3">
-        <v>0</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
+      <c r="U18" s="3">
+        <v>0</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1374,16 +1438,18 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
         <v>-100</v>
@@ -1392,10 +1458,10 @@
         <v>-100</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1407,99 +1473,111 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
+      <c r="U20" s="3">
+        <v>0</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>400</v>
+      </c>
+      <c r="E21" s="3">
+        <v>500</v>
+      </c>
+      <c r="F21" s="3">
         <v>-400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-1100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-1200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-1100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-1100</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>2000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>9300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>6400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>2700</v>
       </c>
-      <c r="S21" s="3">
-        <v>0</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
+      <c r="U21" s="3">
+        <v>0</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1530,11 +1608,11 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1560,78 +1638,90 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F23" s="3">
         <v>-300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-1200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-1100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-1200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>10100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>9100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>6300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>2600</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
+      <c r="U23" s="3">
+        <v>0</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -1645,26 +1735,26 @@
       <c r="I24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="J24" s="3">
+        <v>0</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
+      <c r="N24" s="3">
+        <v>0</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1675,17 +1765,23 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
       </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1746,132 +1842,150 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>-300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-1200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-1200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>10100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>1700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>9100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>6300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>2600</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
+      <c r="U26" s="3">
+        <v>0</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
         <v>-300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-1100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>10100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>1700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>9100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>6300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>2600</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
+      <c r="U27" s="3">
+        <v>0</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1932,8 +2046,14 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1994,8 +2114,14 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2056,8 +2182,14 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2118,16 +2250,22 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
         <v>100</v>
@@ -2136,10 +2274,10 @@
         <v>100</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -2151,99 +2289,111 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
+      <c r="U32" s="3">
+        <v>0</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>-300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-1100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>10100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>1700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>9100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>6300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>2600</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
+      <c r="U33" s="3">
+        <v>0</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2304,137 +2454,155 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>-300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-1100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>10100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>1700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>9100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>6300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>2600</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
+      <c r="U35" s="3">
+        <v>0</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44012</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43830</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43646</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43465</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43281</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2457,8 +2625,10 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2481,59 +2651,61 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>32300</v>
+      </c>
+      <c r="F41" s="3">
         <v>17100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>17100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>17700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>17700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>17200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>17200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>29400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>21600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>17200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>42600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>18200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>9200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>9200</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2543,56 +2715,62 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F42" s="3">
         <v>5300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>5300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>3200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>3200</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>3700</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>2400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>17500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>9800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>1700</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2605,59 +2783,65 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="F43" s="3">
+        <v>0</v>
+      </c>
+      <c r="G43" s="3">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3">
         <v>300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>3500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>3500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>3500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>2100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>300</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2667,23 +2851,29 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>600</v>
+      </c>
+      <c r="F44" s="3">
         <v>1200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1200</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2699,11 +2889,11 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O44" s="3">
         <v>0</v>
@@ -2729,59 +2919,65 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>11800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>11800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>1900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>9000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>9000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>9000</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>2900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>600</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3">
         <v>100</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,59 +2987,65 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>56900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>56900</v>
+      </c>
+      <c r="F46" s="3">
         <v>41900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>41900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>37900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>37900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>42200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>42200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>36100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>38900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>42200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>47200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>39000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>11800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>12200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>9500</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2853,8 +3055,14 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2877,19 +3085,19 @@
         <v>900</v>
       </c>
       <c r="J47" s="3">
-        <v>3700</v>
+        <v>900</v>
       </c>
       <c r="K47" s="3">
         <v>900</v>
       </c>
       <c r="L47" s="3">
+        <v>3700</v>
+      </c>
+      <c r="M47" s="3">
         <v>900</v>
       </c>
-      <c r="M47" s="3">
-        <v>500</v>
-      </c>
       <c r="N47" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="O47" s="3">
         <v>500</v>
@@ -2900,11 +3108,11 @@
       <c r="Q47" s="3">
         <v>500</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
+      <c r="R47" s="3">
+        <v>500</v>
+      </c>
+      <c r="S47" s="3">
+        <v>500</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
@@ -2915,59 +3123,65 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>8500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>8500</v>
+      </c>
+      <c r="F48" s="3">
         <v>8600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>8600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>9200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>9200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>9500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>9500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>9900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>9100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>9500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>500</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2977,59 +3191,65 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3">
         <v>1500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>1100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>800</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3039,8 +3259,14 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3101,8 +3327,14 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3163,8 +3395,14 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3174,18 +3412,18 @@
       <c r="E52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3">
         <v>100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>100</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3195,27 +3433,27 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3">
         <v>1500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>700</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3225,8 +3463,14 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3287,59 +3531,65 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>66500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>66500</v>
+      </c>
+      <c r="F54" s="3">
         <v>53000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>53000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>48600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>48600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>53400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>53400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>50800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>49500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>53400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>50500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>41100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>14400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>14700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>12000</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,8 +3599,14 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3373,8 +3629,10 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3397,59 +3655,61 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F57" s="3">
         <v>2400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>3000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>3000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>2400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>3200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>6100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>300</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3459,8 +3719,14 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3521,59 +3787,65 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>500</v>
+      </c>
+      <c r="F59" s="3">
         <v>600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>600</v>
-      </c>
-      <c r="I59" s="3">
-        <v>600</v>
-      </c>
-      <c r="J59" s="3">
-        <v>1100</v>
       </c>
       <c r="K59" s="3">
         <v>600</v>
       </c>
       <c r="L59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M59" s="3">
         <v>600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
+        <v>600</v>
+      </c>
+      <c r="O59" s="3">
         <v>3700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>1400</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3583,16 +3855,22 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3100</v>
+        <v>1900</v>
       </c>
       <c r="E60" s="3">
-        <v>3100</v>
+        <v>1900</v>
       </c>
       <c r="F60" s="3">
         <v>3100</v>
@@ -3601,41 +3879,41 @@
         <v>3100</v>
       </c>
       <c r="H60" s="3">
+        <v>3100</v>
+      </c>
+      <c r="I60" s="3">
+        <v>3100</v>
+      </c>
+      <c r="J60" s="3">
         <v>3800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>6900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>7500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1700</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3645,8 +3923,14 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3707,8 +3991,14 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3754,11 +4044,11 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R62" s="3">
-        <v>0</v>
-      </c>
-      <c r="S62" s="3">
-        <v>0</v>
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T62" s="3">
         <v>0</v>
@@ -3769,8 +4059,14 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3831,8 +4127,14 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3893,8 +4195,14 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3955,16 +4263,22 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>3100</v>
+        <v>1900</v>
       </c>
       <c r="E66" s="3">
-        <v>3100</v>
+        <v>1900</v>
       </c>
       <c r="F66" s="3">
         <v>3100</v>
@@ -3973,41 +4287,41 @@
         <v>3100</v>
       </c>
       <c r="H66" s="3">
+        <v>3100</v>
+      </c>
+      <c r="I66" s="3">
+        <v>3100</v>
+      </c>
+      <c r="J66" s="3">
         <v>3800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>6900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>7500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1700</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4017,8 +4331,14 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4041,8 +4361,10 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4103,8 +4425,14 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4165,8 +4493,14 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4227,8 +4561,14 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4289,59 +4629,65 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>18600</v>
+      </c>
+      <c r="F72" s="3">
         <v>22400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>22400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>24800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>24800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>28400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>28400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>25200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>26300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>28400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>23800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>13800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>12100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>11700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>8900</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4351,8 +4697,14 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4413,8 +4765,14 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4475,8 +4833,14 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4537,59 +4901,65 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>64600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>64600</v>
+      </c>
+      <c r="F76" s="3">
         <v>49900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>49900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>45500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>45500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>49600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>49600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>47200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>46500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>49600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>43600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>33600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>13300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>13100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>10300</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4599,8 +4969,14 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4661,137 +5037,155 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44012</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43830</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43646</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43465</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43281</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>-300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-1100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>10100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>1700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>9100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>6300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>2600</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
+      <c r="U81" s="3">
+        <v>0</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4814,8 +5208,10 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4831,8 +5227,8 @@
       <c r="G83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H83" s="3">
-        <v>0</v>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
@@ -4843,20 +5239,20 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
@@ -4876,8 +5272,14 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4938,8 +5340,14 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5000,8 +5408,14 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5062,8 +5476,14 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5124,8 +5544,14 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5186,8 +5612,14 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5218,17 +5650,17 @@
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
+        <v>0</v>
       </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
@@ -5248,8 +5680,14 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5272,8 +5710,10 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5304,11 +5744,11 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
@@ -5316,11 +5756,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
@@ -5334,8 +5774,14 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5396,8 +5842,14 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5458,8 +5910,14 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5490,17 +5948,17 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
+        <v>0</v>
       </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
@@ -5520,8 +5978,14 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5544,8 +6008,10 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5576,11 +6042,11 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -5606,8 +6072,14 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5668,8 +6140,14 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5730,8 +6208,14 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5792,8 +6276,14 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5824,17 +6314,17 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
+        <v>0</v>
       </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
@@ -5854,8 +6344,14 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5871,32 +6367,32 @@
       <c r="G101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
       </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
@@ -5916,8 +6412,14 @@
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5954,11 +6456,11 @@
       <c r="N102" s="3">
         <v>0</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
       </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
@@ -5976,6 +6478,12 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
